--- a/reid_openset/tables/best_threshold_rank.xlsx
+++ b/reid_openset/tables/best_threshold_rank.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <name val="Times New Roman"/>
@@ -67,6 +64,12 @@
       <bottom style="thin"/>
     </border>
     <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="medium"/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin"/>
@@ -87,41 +90,30 @@
       <bottom style="thin"/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="medium"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -488,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -501,86 +493,92 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Backbone</t>
-        </is>
-      </c>
+      <c r="A1" s="1" t="n"/>
       <c r="B1" s="2" t="inlineStr">
         <is>
           <t>DINOv3-ViT-B/16</t>
         </is>
       </c>
-      <c r="C1" s="2" t="n"/>
+      <c r="C1" s="3" t="n"/>
       <c r="D1" s="2" t="inlineStr">
         <is>
           <t>MegaDescriptor-L-384</t>
         </is>
       </c>
-      <c r="E1" s="2" t="n"/>
+      <c r="E1" s="3" t="n"/>
       <c r="F1" s="2" t="inlineStr">
         <is>
           <t>BioCLIP-2 ViT-L/14</t>
         </is>
       </c>
-      <c r="G1" s="2" t="n"/>
+      <c r="G1" s="3" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Split</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Examples per individual</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Validation</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Validation</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Validation</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Examples per individual</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="n"/>
-      <c r="C3" s="6" t="n"/>
-      <c r="D3" s="6" t="n"/>
-      <c r="E3" s="6" t="n"/>
-      <c r="F3" s="6" t="n"/>
-      <c r="G3" s="6" t="n"/>
+      <c r="A3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E3" s="7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F3" s="7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G3" s="7" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
-        <v>2</v>
+      <c r="A4" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>0.5</v>
@@ -589,7 +587,7 @@
         <v>0.2</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="F4" s="7" t="n">
         <v>0.3</v>
@@ -599,31 +597,31 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
-        <v>4</v>
+      <c r="A5" s="6" t="n">
+        <v>8</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>0.5</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
-        <v>8</v>
+      <c r="A6" s="6" t="n">
+        <v>16</v>
       </c>
       <c r="B6" s="7" t="n">
         <v>0.4</v>
@@ -645,31 +643,31 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
-        <v>16</v>
+      <c r="A7" s="6" t="n">
+        <v>32</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>0.5</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
-        <v>32</v>
+      <c r="A8" s="6" t="n">
+        <v>64</v>
       </c>
       <c r="B8" s="7" t="n">
         <v>0.5</v>
@@ -678,38 +676,15 @@
         <v>0.5</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="n">
-        <v>64</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
         <v>0</v>
       </c>
     </row>
